--- a/output/pdf_financials_xlsx/MKA.xlsx
+++ b/output/pdf_financials_xlsx/MKA.xlsx
@@ -1482,16 +1482,16 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.856908</v>
+        <v>-0.856908</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.529181</v>
+        <v>-2.529181</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>7.176128</v>
+        <v>-7.176128</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>3.039236</v>
+        <v>-3.039236</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>-4.067786</v>
@@ -1826,16 +1826,16 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.856908</v>
+        <v>-0.856908</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.529181</v>
+        <v>-2.529181</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>7.176128</v>
+        <v>-7.176128</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>3.039236</v>
+        <v>-3.039236</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>-4.067786</v>
@@ -2034,16 +2034,16 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.856908</v>
+        <v>-0.856908</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.529181</v>
+        <v>-2.529181</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>7.176128</v>
+        <v>-7.176128</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>3.039236</v>
+        <v>-3.039236</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>-4.067786</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>87.213138</v>
+        <v>-87.213138</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-233.787385</v>
+        <v>233.787385</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>239.281529</v>
@@ -2332,16 +2332,16 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.856908</v>
+        <v>-0.856908</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>2.529181</v>
+        <v>-2.529181</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>7.176128</v>
+        <v>-7.176128</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>3.039236</v>
+        <v>-3.039236</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-4.067786</v>
@@ -2470,16 +2470,16 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.867765</v>
+        <v>-0.846051</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.540335</v>
+        <v>-2.518027</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>7.202034</v>
+        <v>-7.150222</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>3.069065</v>
+        <v>-3.009407</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-4.036442</v>
@@ -2644,16 +2644,16 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-0</v>
@@ -7170,7 +7170,7 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>0.856908</v>
+        <v>-0.856908</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-2.529181</v>
@@ -7179,7 +7179,7 @@
         <v>-7.176128</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>3.039236</v>
+        <v>-3.039236</v>
       </c>
       <c r="O99" s="3" t="n">
         <v>-4.067786</v>
@@ -7419,10 +7419,10 @@
         <v>0</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.207864</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.097398</v>
       </c>
       <c r="H103" s="3" t="n">
         <v>0.054713</v>
@@ -7617,10 +7617,10 @@
         <v>0.780257</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.654508</v>
+        <v>-0.862372</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.011094</v>
+        <v>0.108492</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>0.054713</v>
@@ -24703,7 +24703,11 @@
           <t>Prepaid and deposit</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -50844,7 +50848,11 @@
           <t>Prepaid and deposit</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -64069,16 +64077,16 @@
         </is>
       </c>
       <c r="N495" s="5" t="n">
-        <v>0.856908</v>
+        <v>-0.856908</v>
       </c>
       <c r="O495" s="5" t="n">
-        <v>2.529181</v>
+        <v>-2.529181</v>
       </c>
       <c r="P495" s="5" t="n">
-        <v>7.176128</v>
+        <v>-7.176128</v>
       </c>
       <c r="Q495" s="5" t="n">
-        <v>3.039236</v>
+        <v>-3.039236</v>
       </c>
       <c r="R495" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MKA.xlsx
+++ b/output/pdf_financials_xlsx/MKA.xlsx
@@ -1070,16 +1070,16 @@
         <v>9.529149</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>5.872552</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>4.493522</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0</v>
+        <v>3.199774</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>0</v>
+        <v>6.893534</v>
       </c>
     </row>
     <row r="11">
@@ -1188,52 +1188,52 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001737</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.014151</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002373</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-1.5e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000346</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-8e-06</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-7e-06</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-9e-06</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001013</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-9.8e-05</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008640999999999999</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011134</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>2.5e-05</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>5.3e-05</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>1.4e-05</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>0</v>
+        <v>1.3e-05</v>
       </c>
     </row>
     <row r="13">
@@ -2310,16 +2310,16 @@
         <v>-0.007048</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.318741</v>
+        <v>-0.317004</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.407339</v>
+        <v>-3.393188</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.858643</v>
+        <v>-2.85627</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.897893</v>
+        <v>-1.897878</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2332,34 +2332,34 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.856908</v>
+        <v>-0.856901</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.529181</v>
+        <v>-2.529172</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-7.176128</v>
+        <v>-7.175115</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.039236</v>
+        <v>-3.039138</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.067786</v>
+        <v>-4.059145</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-9.707072999999999</v>
+        <v>-9.695938999999999</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-5.985963</v>
+        <v>-5.985988</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-4.120854</v>
+        <v>-4.120907</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.278037</v>
+        <v>-0.278051</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>-17.503758</v>
+        <v>-17.503771</v>
       </c>
     </row>
     <row r="28">
@@ -2448,16 +2448,16 @@
         <v>-0.007048</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.318741</v>
+        <v>-0.317004</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.406094</v>
+        <v>-3.391943</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.856181</v>
+        <v>-2.853808</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.896631</v>
+        <v>-1.896616</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -2470,34 +2470,34 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.846051</v>
+        <v>-0.846044</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.518027</v>
+        <v>-2.518018</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-7.150222</v>
+        <v>-7.149209</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.009407</v>
+        <v>-3.009309</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.036442</v>
+        <v>-4.027801</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-9.675528999999999</v>
+        <v>-9.664395000000001</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-5.967569</v>
+        <v>-5.967594</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-4.087994</v>
+        <v>-4.088047</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.086684</v>
+        <v>-0.086698</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>-17.163159</v>
+        <v>-17.163172</v>
       </c>
     </row>
     <row r="30">
@@ -2825,16 +2825,16 @@
         <v>0.691276</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.391964</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>9.530017000000001</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>4.924567</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>4.44685</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>0.493703</v>
@@ -2957,16 +2957,16 @@
         <v>0.691276</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.391964</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>9.530017000000001</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>4.924567</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>4.44685</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>0.493703</v>
@@ -3749,16 +3749,16 @@
         <v>0.010338</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.610202</v>
+        <v>0.218238</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>9.730632999999999</v>
+        <v>0.200616</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>5.026114</v>
+        <v>0.101547</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>4.542998</v>
+        <v>0.096148</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0.162522</v>
@@ -8852,7 +8852,7 @@
         <v>0</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.070116</v>
       </c>
       <c r="T124" s="3" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
         <v>0</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.070116</v>
       </c>
       <c r="T125" s="3" t="n">
         <v>0</v>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -33127,7 +33127,11 @@
           <t>Lease payments 17</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -57132,7 +57136,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -57211,16 +57215,16 @@
         </is>
       </c>
       <c r="T431" s="5" t="n">
-        <v>-5.872552</v>
+        <v>5.872552</v>
       </c>
       <c r="U431" s="5" t="n">
-        <v>-4.493522</v>
+        <v>4.493522</v>
       </c>
       <c r="V431" s="5" t="n">
-        <v>-3.199774</v>
+        <v>3.199774</v>
       </c>
       <c r="W431" s="5" t="n">
-        <v>-6.893534</v>
+        <v>6.893534</v>
       </c>
     </row>
     <row r="432">
@@ -57356,7 +57360,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -67211,7 +67215,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -68987,7 +68991,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">

--- a/output/pdf_financials_xlsx/MKA.xlsx
+++ b/output/pdf_financials_xlsx/MKA.xlsx
@@ -2419,13 +2419,13 @@
         <v>0.018394</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.03286</v>
+        <v>0.220249</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0.191353</v>
+        <v>0.533849</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>0.340599</v>
+        <v>0.532392</v>
       </c>
     </row>
     <row r="29">
@@ -2491,13 +2491,13 @@
         <v>-5.967594</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-4.088047</v>
+        <v>-3.900658</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.086698</v>
+        <v>0.255798</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>-17.163172</v>
+        <v>-16.971379</v>
       </c>
     </row>
     <row r="30">
@@ -7257,13 +7257,13 @@
         <v>0</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.220249</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>0.533849</v>
       </c>
       <c r="T100" s="3" t="n">
-        <v>0</v>
+        <v>0.532392</v>
       </c>
     </row>
     <row r="101">
@@ -28997,7 +28997,11 @@
           <t>Amortisation of intangible assets 12</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -32685,7 +32689,11 @@
           <t>Amortisation of intangible assets 11</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -34909,7 +34917,11 @@
           <t>Amortisation of intangible assets 7</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MKA.xlsx
+++ b/output/pdf_financials_xlsx/MKA.xlsx
@@ -4852,25 +4852,25 @@
         <v>0</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.309002</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.098567</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>1.011257</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.574068</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.277302</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0</v>
+        <v>0.405234</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>0</v>
+        <v>1.144688</v>
       </c>
     </row>
     <row r="65">
@@ -5050,25 +5050,25 @@
         <v>0</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.095051</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.15098</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.205098</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.09286899999999999</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.047063</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.046769</v>
       </c>
       <c r="T67" s="3" t="n">
-        <v>0</v>
+        <v>0.047688</v>
       </c>
     </row>
     <row r="68">
@@ -7899,10 +7899,10 @@
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>-0.068271</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.024512</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>0</v>
@@ -8310,16 +8310,16 @@
         <v>0</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-0.170351</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>0</v>
+        <v>-0.481401</v>
       </c>
       <c r="S116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T116" s="3" t="n">
-        <v>0</v>
+        <v>-0.204404</v>
       </c>
     </row>
     <row r="117">
@@ -29883,7 +29883,11 @@
           <t>Deferred tax recovery 25</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -30610,7 +30614,11 @@
           <t>Acquisition of intangible assets 12</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -33583,7 +33591,11 @@
           <t>Deferred tax recovery 23</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -35470,7 +35482,11 @@
           <t>Acquisition of intangible assets 7</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -41929,7 +41945,11 @@
           <t>Accretion 6</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -70000,7 +70020,11 @@
           <t>Interest revenue $ 1,999 $</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E549" s="5" t="n">
         <v>0.004339</v>
       </c>
